--- a/artfynd/A 41600-2024 artfynd.xlsx
+++ b/artfynd/A 41600-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122745011</v>
       </c>
       <c r="B2" t="n">
-        <v>92221</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745000</v>
+        <v>122745002</v>
       </c>
       <c r="B3" t="n">
-        <v>92221</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Säckberget NV, Ång</t>
+          <t>Stormyran S, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699493</v>
+        <v>699533</v>
       </c>
       <c r="R3" t="n">
-        <v>7044615</v>
+        <v>7044684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745002</v>
+        <v>122745000</v>
       </c>
       <c r="B4" t="n">
-        <v>90958</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stormyran S, Ång</t>
+          <t>Säckberget NV, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699533</v>
+        <v>699493</v>
       </c>
       <c r="R4" t="n">
-        <v>7044684</v>
+        <v>7044615</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41600-2024 artfynd.xlsx
+++ b/artfynd/A 41600-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745011</v>
+        <v>122745002</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Naturres. N, Ång</t>
+          <t>Stormyran S, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699706</v>
+        <v>699533</v>
       </c>
       <c r="R2" t="n">
-        <v>7044520</v>
+        <v>7044684</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester, Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745002</v>
+        <v>122745000</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stormyran S, Ång</t>
+          <t>Säckberget NV, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699533</v>
+        <v>699493</v>
       </c>
       <c r="R3" t="n">
-        <v>7044684</v>
+        <v>7044615</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester, Helene Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745000</v>
+        <v>122745011</v>
       </c>
       <c r="B4" t="n">
         <v>92225</v>
@@ -923,14 +923,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Säckberget NV, Ång</t>
+          <t>Naturres. N, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699493</v>
+        <v>699706</v>
       </c>
       <c r="R4" t="n">
-        <v>7044615</v>
+        <v>7044520</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester, Helene Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 41600-2024 artfynd.xlsx
+++ b/artfynd/A 41600-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745002</v>
+        <v>122745011</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stormyran S, Ång</t>
+          <t>Naturres. N, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699533</v>
+        <v>699706</v>
       </c>
       <c r="R2" t="n">
-        <v>7044684</v>
+        <v>7044520</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristofer Wester, Helene Andersson</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristofer Wester, Helene Andersson</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745011</v>
+        <v>122745002</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Naturres. N, Ång</t>
+          <t>Stormyran S, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699706</v>
+        <v>699533</v>
       </c>
       <c r="R4" t="n">
-        <v>7044520</v>
+        <v>7044684</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristofer Wester, Helene Andersson</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 41600-2024 artfynd.xlsx
+++ b/artfynd/A 41600-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745011</v>
+        <v>122745002</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Naturres. N, Ång</t>
+          <t>Stormyran S, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699706</v>
+        <v>699533</v>
       </c>
       <c r="R2" t="n">
-        <v>7044520</v>
+        <v>7044684</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745000</v>
+        <v>122745011</v>
       </c>
       <c r="B3" t="n">
         <v>92225</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Säckberget NV, Ång</t>
+          <t>Naturres. N, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699493</v>
+        <v>699706</v>
       </c>
       <c r="R3" t="n">
-        <v>7044615</v>
+        <v>7044520</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745002</v>
+        <v>122745000</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stormyran S, Ång</t>
+          <t>Säckberget NV, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699533</v>
+        <v>699493</v>
       </c>
       <c r="R4" t="n">
-        <v>7044684</v>
+        <v>7044615</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41600-2024 artfynd.xlsx
+++ b/artfynd/A 41600-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122745002</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745011</v>
+        <v>122745000</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
+        <v>92233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Naturres. N, Ång</t>
+          <t>Säckberget NV, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699706</v>
+        <v>699493</v>
       </c>
       <c r="R3" t="n">
-        <v>7044520</v>
+        <v>7044615</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745000</v>
+        <v>122745011</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>92233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,14 +923,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Säckberget NV, Ång</t>
+          <t>Naturres. N, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699493</v>
+        <v>699706</v>
       </c>
       <c r="R4" t="n">
-        <v>7044615</v>
+        <v>7044520</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41600-2024 artfynd.xlsx
+++ b/artfynd/A 41600-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745002</v>
+        <v>122745000</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>92233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stormyran S, Ång</t>
+          <t>Säckberget NV, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699533</v>
+        <v>699493</v>
       </c>
       <c r="R2" t="n">
-        <v>7044684</v>
+        <v>7044615</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745000</v>
+        <v>122745002</v>
       </c>
       <c r="B3" t="n">
-        <v>92233</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Säckberget NV, Ång</t>
+          <t>Stormyran S, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699493</v>
+        <v>699533</v>
       </c>
       <c r="R3" t="n">
-        <v>7044615</v>
+        <v>7044684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 41600-2024 artfynd.xlsx
+++ b/artfynd/A 41600-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745000</v>
+        <v>122745011</v>
       </c>
       <c r="B2" t="n">
         <v>92233</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Säckberget NV, Ång</t>
+          <t>Naturres. N, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699493</v>
+        <v>699706</v>
       </c>
       <c r="R2" t="n">
-        <v>7044615</v>
+        <v>7044520</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745002</v>
+        <v>122745000</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>92233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stormyran S, Ång</t>
+          <t>Säckberget NV, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699533</v>
+        <v>699493</v>
       </c>
       <c r="R3" t="n">
-        <v>7044684</v>
+        <v>7044615</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745011</v>
+        <v>122745002</v>
       </c>
       <c r="B4" t="n">
-        <v>92233</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Naturres. N, Ång</t>
+          <t>Stormyran S, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699706</v>
+        <v>699533</v>
       </c>
       <c r="R4" t="n">
-        <v>7044520</v>
+        <v>7044684</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41600-2024 artfynd.xlsx
+++ b/artfynd/A 41600-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745011</v>
+        <v>122745000</v>
       </c>
       <c r="B2" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Naturres. N, Ång</t>
+          <t>Säckberget NV, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699706</v>
+        <v>699493</v>
       </c>
       <c r="R2" t="n">
-        <v>7044520</v>
+        <v>7044615</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745000</v>
+        <v>122745011</v>
       </c>
       <c r="B3" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Säckberget NV, Ång</t>
+          <t>Naturres. N, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699493</v>
+        <v>699706</v>
       </c>
       <c r="R3" t="n">
-        <v>7044615</v>
+        <v>7044520</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122745002</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41600-2024 artfynd.xlsx
+++ b/artfynd/A 41600-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122745000</v>
       </c>
       <c r="B2" t="n">
-        <v>92236</v>
+        <v>92238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745011</v>
+        <v>122745002</v>
       </c>
       <c r="B3" t="n">
-        <v>92236</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Naturres. N, Ång</t>
+          <t>Stormyran S, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699706</v>
+        <v>699533</v>
       </c>
       <c r="R3" t="n">
-        <v>7044520</v>
+        <v>7044684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745002</v>
+        <v>122745011</v>
       </c>
       <c r="B4" t="n">
-        <v>90973</v>
+        <v>92238</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stormyran S, Ång</t>
+          <t>Naturres. N, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699533</v>
+        <v>699706</v>
       </c>
       <c r="R4" t="n">
-        <v>7044684</v>
+        <v>7044520</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
